--- a/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Lunes 2 diciembre/2 de Diciembre.xlsx
+++ b/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Lunes 2 diciembre/2 de Diciembre.xlsx
@@ -1,33 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\Evaluacion2\noviembre\Lunes 2 diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346D25E4-3D5B-493F-A258-E950B51952DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416592B6-06FA-4B42-829D-DD95E50CFB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{AE2FB389-9F98-41F7-876B-EB4FCB256BB9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{AE2FB389-9F98-41F7-876B-EB4FCB256BB9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Menu" sheetId="4" r:id="rId1"/>
+    <sheet name="Ejercicio 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Ejercicio 2" sheetId="1" r:id="rId3"/>
+    <sheet name="Ejercicio 3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+  <si>
+    <t>MATRIZ</t>
+  </si>
+  <si>
+    <t>FIAT</t>
+  </si>
+  <si>
+    <t>AUDI</t>
+  </si>
+  <si>
+    <t>BMW</t>
+  </si>
+  <si>
+    <t>SEAT</t>
+  </si>
   <si>
     <t>Código Producto</t>
   </si>
@@ -62,22 +89,106 @@
     <t>Existencia</t>
   </si>
   <si>
-    <t>MATRIZ</t>
-  </si>
-  <si>
-    <t>FIAT</t>
-  </si>
-  <si>
-    <t>AUDI</t>
-  </si>
-  <si>
-    <t>BMW</t>
-  </si>
-  <si>
-    <t>SEAT</t>
-  </si>
-  <si>
-    <t>explica buscar x y muestra un ejemplo</t>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Abr</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>Cual es el prefijo del país?</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>BD</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>+86</t>
+  </si>
+  <si>
+    <t>+91</t>
+  </si>
+  <si>
+    <t>+1</t>
+  </si>
+  <si>
+    <t>+62</t>
+  </si>
+  <si>
+    <t>+55</t>
+  </si>
+  <si>
+    <t>+92</t>
+  </si>
+  <si>
+    <t>+234</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+7</t>
+  </si>
+  <si>
+    <t>+52</t>
   </si>
 </sst>
 </file>
@@ -108,7 +219,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,8 +255,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -194,19 +317,154 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -219,13 +477,82 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -335,13 +662,10 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Hoja2!$C$2:$C$3</c:f>
+              <c:f>'Ejercicio 1'!$C$3</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>MATRIZ</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>2010</c:v>
                 </c:pt>
               </c:strCache>
@@ -428,7 +752,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Hoja2!$B$4:$B$7</c:f>
+              <c:f>'Ejercicio 1'!$B$4:$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -448,7 +772,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Hoja2!$C$4:$C$7</c:f>
+              <c:f>'Ejercicio 1'!$C$4:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -478,13 +802,10 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Hoja2!$D$2:$D$3</c:f>
+              <c:f>'Ejercicio 1'!$D$3</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>MATRIZ</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>2012</c:v>
                 </c:pt>
               </c:strCache>
@@ -571,7 +892,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Hoja2!$B$4:$B$7</c:f>
+              <c:f>'Ejercicio 1'!$B$4:$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -591,7 +912,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Hoja2!$D$4:$D$7</c:f>
+              <c:f>'Ejercicio 1'!$D$4:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1359,6 +1680,314 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>151086</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>32845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>656897</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>197069</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectángulo 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0112A593-88F1-E271-1597-6D31E7044842}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6036879" y="1333500"/>
+          <a:ext cx="1346639" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>EJERCICIOS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>93280</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>211520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>599091</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>158968</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectángulo 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{749DA99C-A810-41D1-9F5C-9A3C387D735D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7660728" y="1945727"/>
+          <a:ext cx="1346639" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent6"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>EJERCICIO</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200" baseline="0"/>
+            <a:t> 3</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1600" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>258818</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>212835</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>764629</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>160283</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectángulo 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90D612D1-45C6-409A-90DE-3616194D8B9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6144611" y="1947042"/>
+          <a:ext cx="1346639" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent4"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>EJERCICIO</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200" baseline="0"/>
+            <a:t> 2</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1600" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>207579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>122184</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>155027</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectángulo 4">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90C9EF89-8BF6-4A15-AEAE-904A6E4476F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4661338" y="1941786"/>
+          <a:ext cx="1346639" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent5"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>EJERCICIO</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200" baseline="0"/>
+            <a:t> 1</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1600" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>149019</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -1367,8 +1996,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>103908</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1396,15 +2025,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>704850</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>809625</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1419,8 +2048,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6819900" y="3590925"/>
-          <a:ext cx="8286750" cy="2428875"/>
+          <a:off x="6696075" y="1781176"/>
+          <a:ext cx="6000750" cy="3543300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1486,9 +2115,314 @@
             <a:t>4. Para finalizar la marca Seat presenta ganancias de 230 unidades después de 2 años.</a:t>
           </a:r>
         </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>990600</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Flecha: hacia la izquierda 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F027563-32B0-46DC-9CD8-9B8E743F7BA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="276225" y="5267325"/>
+          <a:ext cx="885825" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 75000"/>
+            <a:gd name="adj2" fmla="val 52500"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1200"/>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>Volver</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13138</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>118242</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>898963</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>65690</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Flecha: hacia la izquierda 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71A236F9-2971-4EE5-8DB5-9ABF6F045A47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="203638" y="3915104"/>
+          <a:ext cx="885825" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 75000"/>
+            <a:gd name="adj2" fmla="val 52500"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>Volver</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>791308</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>190502</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>58615</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>7328</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectángulo 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AF3514F-8FCB-471A-8EFB-C7B8487D860E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2659673" y="732694"/>
+          <a:ext cx="1773115" cy="1135672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent6"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1200" baseline="0"/>
+            <a:t>La función </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1200" b="1" baseline="0"/>
+            <a:t>buscarx()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1200" b="0" baseline="0"/>
+            <a:t> consiste en la búsqueda de un rango o matriz y a posteriori muestra el primer valor que encuentre.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1200" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>36634</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>73269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>72536</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>14653</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Flecha: hacia la izquierda 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{254B0823-747E-408E-93DE-71D55A2D3D5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="351692" y="2813538"/>
+          <a:ext cx="885825" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 75000"/>
+            <a:gd name="adj2" fmla="val 52500"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1600" kern="1200"/>
+            <a:t>Volver</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1760,77 +2694,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6C5DE3-1D89-4BF9-9E8F-351003E16526}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4723F3-65BB-4118-B6B1-9222BEE8DDFE}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="B2:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="29.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11" style="3"/>
-    <col min="6" max="6" width="19.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.5" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="11" style="3"/>
+    <col min="1" max="1" width="2.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1"/>
+    <col min="6" max="6" width="19.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B3" s="7"/>
-      <c r="C3" s="5">
+      <c r="B3" s="5"/>
+      <c r="C3" s="3">
         <v>2010</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>2012</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
         <v>150</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>155</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
         <v>250</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>180</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
         <v>320</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
         <v>125</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>355</v>
       </c>
     </row>
@@ -1843,245 +2793,395 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2ABB058-C764-4581-A990-E1FD8E72A4AF}">
+  <sheetPr>
+    <tabColor theme="7"/>
+  </sheetPr>
   <dimension ref="B2:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="23.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="3"/>
+    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="2" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="14">
         <v>112434678</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="15">
         <v>223745544</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="15">
         <v>233345567</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="15">
         <v>234456543</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="15">
         <v>332345667</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="15">
         <v>334543217</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="15">
         <v>443456321</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="16">
         <v>492123213</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
+    <row r="3" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="E3" s="8" t="s">
         <v>9</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2">
+      <c r="C4" s="17">
+        <v>15</v>
+      </c>
+      <c r="D4" s="18">
         <v>5543</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="18">
         <v>66</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="18">
         <v>65</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="18">
         <v>998</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="18">
         <v>12</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="18">
         <v>78</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="19">
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
+    <row r="7" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="2:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="4">
+      <c r="B9" s="21">
         <v>443456321</v>
       </c>
-      <c r="C9" s="4" t="str">
+      <c r="C9" s="1" t="str">
         <f>HLOOKUP(B9,$C$2:$J$4,2,FALSE)</f>
         <v>MEMORIA SD 32 GB</v>
       </c>
-      <c r="D9" s="4">
-        <f>HLOOKUP(B9,$C$2:$J$4,3,FALSE)</f>
+      <c r="D9" s="22">
+        <f t="shared" ref="D9:D16" si="0">HLOOKUP(B9,$C$2:$J$4,3,FALSE)</f>
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="4">
+      <c r="B10" s="21">
         <v>332345667</v>
       </c>
-      <c r="C10" s="4" t="str">
-        <f t="shared" ref="C10:C16" si="0">HLOOKUP(B10,$C$2:$J$4,2,FALSE)</f>
+      <c r="C10" s="1" t="str">
+        <f t="shared" ref="C10:C16" si="1">HLOOKUP(B10,$C$2:$J$4,2,FALSE)</f>
         <v>ALFOMBRA VERDE</v>
       </c>
-      <c r="D10" s="4">
-        <f>HLOOKUP(B10,$C$2:$J$4,3,FALSE)</f>
+      <c r="D10" s="22">
+        <f t="shared" si="0"/>
         <v>998</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="4">
+      <c r="B11" s="21">
         <v>223745544</v>
       </c>
-      <c r="C11" s="4" t="str">
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>REGULADOR DE VOLTAGE</v>
+      </c>
+      <c r="D11" s="22">
         <f t="shared" si="0"/>
-        <v>REGULADOR DE VOLTAGE</v>
-      </c>
-      <c r="D11" s="4">
-        <f>HLOOKUP(B11,$C$2:$J$4,3,FALSE)</f>
         <v>5543</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="4">
+      <c r="B12" s="21">
         <v>112434678</v>
       </c>
-      <c r="C12" s="4" t="str">
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>SILLA ERGONÓMICA</v>
+      </c>
+      <c r="D12" s="22">
         <f t="shared" si="0"/>
-        <v>SILLA ERGONÓMICA</v>
-      </c>
-      <c r="D12" s="4">
-        <f>HLOOKUP(B12,$C$2:$J$4,3,FALSE)</f>
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="4">
+      <c r="B13" s="21">
         <v>233345567</v>
       </c>
-      <c r="C13" s="4" t="str">
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>LAMPARA ESCRITORIO</v>
+      </c>
+      <c r="D13" s="22">
         <f t="shared" si="0"/>
-        <v>LAMPARA ESCRITORIO</v>
-      </c>
-      <c r="D13" s="4">
-        <f>HLOOKUP(B13,$C$2:$J$4,3,FALSE)</f>
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="4">
+      <c r="B14" s="21">
         <v>492123213</v>
       </c>
-      <c r="C14" s="4" t="str">
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>CABLE USB</v>
+      </c>
+      <c r="D14" s="22">
         <f t="shared" si="0"/>
-        <v>CABLE USB</v>
-      </c>
-      <c r="D14" s="4">
-        <f>HLOOKUP(B14,$C$2:$J$4,3,FALSE)</f>
         <v>432</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="4">
+      <c r="B15" s="21">
         <v>234456543</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>ALFOMBRA AZUL</v>
+      </c>
+      <c r="D15" s="22">
         <f t="shared" si="0"/>
-        <v>ALFOMBRA AZUL</v>
-      </c>
-      <c r="D15" s="4">
-        <f>HLOOKUP(B15,$C$2:$J$4,3,FALSE)</f>
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="4">
+      <c r="B16" s="23">
         <v>334543217</v>
       </c>
-      <c r="C16" s="4" t="str">
+      <c r="C16" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>PROYECTOR PORTATIL</v>
+      </c>
+      <c r="D16" s="25">
         <f t="shared" si="0"/>
-        <v>PROYECTOR PORTATIL</v>
-      </c>
-      <c r="D16" s="4">
-        <f>HLOOKUP(B16,$C$2:$J$4,3,FALSE)</f>
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C57AEB-1C9F-4E9C-A91C-BDF355E1F3F0}">
-  <dimension ref="B1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="B1:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="1" max="1" width="4.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11" style="1"/>
+    <col min="8" max="8" width="11" style="8"/>
+    <col min="9" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
         <v>16</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="10" t="str">
+        <f>B3</f>
+        <v>China</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(F3,B3:B12,D3:D12)</f>
+        <v>+86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F2:G2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D3 D4:D13" numberStoredAsText="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>